--- a/results/0916-all/晋东豫西丘陵山地农林牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/晋东豫西丘陵山地农林牧区/tech_selected_summary.xlsx
@@ -253,184 +253,184 @@
     <t>左权县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 35087.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>35087.22</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
@@ -481,7 +481,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 102267550.81</t>
+    <t>102267550.81</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -505,7 +505,7 @@
     <t>4R(Right time)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 11938074.44</t>
+    <t>11938074.44</t>
   </si>
   <si>
     <t>Feed processing_beef cattle</t>
@@ -547,7 +547,7 @@
     <t>4R(Right type)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 137962672.36</t>
+    <t>137962672.36</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -577,16 +577,16 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 109103262.41</t>
+    <t>109103262.41</t>
   </si>
   <si>
     <t>rolller press_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 52603961.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 3227881.15</t>
+    <t>52603961.76</t>
+  </si>
+  <si>
+    <t>3227881.15</t>
   </si>
   <si>
     <t>EEF(NI)_rice</t>
@@ -598,13 +598,13 @@
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 188299318.07</t>
+    <t>188299318.07</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 13110716.50</t>
+    <t>13110716.50</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -628,22 +628,22 @@
     <t>incorporation_pig</t>
   </si>
   <si>
-    <t>总经济成本: 202629207.26</t>
+    <t>202629207.26</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 81888828.20</t>
+    <t>81888828.20</t>
   </si>
   <si>
     <t>chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 22761861.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 2771536.48</t>
+    <t>22761861.58</t>
+  </si>
+  <si>
+    <t>2771536.48</t>
   </si>
   <si>
     <t>chemical amendments_beef cattle</t>
@@ -670,22 +670,22 @@
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 588842528.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 4693004.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 49320270.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 4257999.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 160088727.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 157422419.68</t>
+    <t>588842528.35</t>
+  </si>
+  <si>
+    <t>4693004.09</t>
+  </si>
+  <si>
+    <t>49320270.77</t>
+  </si>
+  <si>
+    <t>4257999.85</t>
+  </si>
+  <si>
+    <t>160088727.18</t>
+  </si>
+  <si>
+    <t>157422419.68</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -694,7 +694,7 @@
     <t>surface crust cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 133053554.83</t>
+    <t>133053554.83</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -709,16 +709,16 @@
     <t>nitrification inhibitor_pig</t>
   </si>
   <si>
-    <t>总经济成本: 274248288.04</t>
+    <t>274248288.04</t>
   </si>
   <si>
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 383121645.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 14255362.65</t>
+    <t>383121645.22</t>
+  </si>
+  <si>
+    <t>14255362.65</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
@@ -727,10 +727,10 @@
     <t>residue rerention_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 52790305.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 3876212.19</t>
+    <t>52790305.10</t>
+  </si>
+  <si>
+    <t>3876212.19</t>
   </si>
 </sst>
 </file>
